--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.49174310308997</v>
+        <v>5.60490825425212</v>
       </c>
       <c r="D2" t="n">
-        <v>34.38402473323988</v>
+        <v>5.58740401915148</v>
       </c>
       <c r="E2" t="n">
-        <v>20.27303768940904</v>
+        <v>3.294368624528969</v>
       </c>
       <c r="F2" t="n">
-        <v>14.45563563991847</v>
+        <v>2.349040791486752</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.6202742103151</v>
+        <v>9.525794559176205</v>
       </c>
       <c r="D3" t="n">
-        <v>44.99198207009695</v>
+        <v>7.311197086390754</v>
       </c>
       <c r="E3" t="n">
-        <v>20.27303768940904</v>
+        <v>3.294368624528969</v>
       </c>
       <c r="F3" t="n">
-        <v>14.45563563991847</v>
+        <v>2.349040791486752</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>76.60693105442047</v>
+        <v>12.44862629634333</v>
       </c>
       <c r="D4" t="n">
-        <v>43.69164477500183</v>
+        <v>7.099892275937797</v>
       </c>
       <c r="E4" t="n">
-        <v>20.27303768940904</v>
+        <v>3.294368624528969</v>
       </c>
       <c r="F4" t="n">
-        <v>14.45563563991847</v>
+        <v>2.349040791486752</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.7696571661074</v>
+        <v>3.862569289492453</v>
       </c>
       <c r="D5" t="n">
-        <v>24.2292106322713</v>
+        <v>3.937246727744086</v>
       </c>
       <c r="E5" t="n">
-        <v>20.27303768940904</v>
+        <v>3.294368624528969</v>
       </c>
       <c r="F5" t="n">
-        <v>14.45563563991847</v>
+        <v>2.349040791486752</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>69.43174021774033</v>
+        <v>11.2826577853828</v>
       </c>
       <c r="D6" t="n">
-        <v>67.7750704395407</v>
+        <v>11.01344894642536</v>
       </c>
       <c r="E6" t="n">
-        <v>20.27303768940904</v>
+        <v>3.294368624528969</v>
       </c>
       <c r="F6" t="n">
-        <v>14.45563563991847</v>
+        <v>2.349040791486752</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
